--- a/manuscript/_m/manuscript_supplement/supplementary_data/dataS08_projection_sign_scale.xlsx
+++ b/manuscript/_m/manuscript_supplement/supplementary_data/dataS08_projection_sign_scale.xlsx
@@ -483,7 +483,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>One row per method, transfer direction and region pair, with the switch-axis sign convention appended to the IsoGraph rows. The two arms are counted over different denominators and both are given: raw sign agreement over the modules whose projected age correlation is significant in both cohorts, and standardized sign agreement over every age-testable module. The raw arm is the reason the reported statistic is standardized – it is near-unanimous within a region and can be unanimous in either direction (8 of 8, 8 of 8 and 0 of 13 for the three BrainSEQ-to-GTEx pairs), which tracks the target cohort's own age-correlated structure rather than the modules. The orientation columns give the second reason: the switch axis of a gene is fitted independently in each cohort, and about 45% of the genes that can be oriented (2,505-2,616 of 5,450-5,739 per region) carry the opposite sign in the two cohorts, so a raw projected coefficient inherits a sign the projection did not earn. These columns are empty for WGCNA, which projects abundance features and has no switch axis to orient.</t>
+          <t>One row per method, transfer direction and region pair, with the switch-axis sign convention appended to the IsoGraph rows. The two arms are counted over different denominators and both are given: raw sign agreement over the modules whose projected age correlation is significant in both cohorts, and standardized sign agreement over every age-testable module. The raw arm is the reason the reported statistic is standardized – it is near-unanimous within a region and can be unanimous in either direction (8 of 8, 8 of 8 and 0 of 13 for the three BrainSEQ-to-GTEx pairs), which tracks the target cohort's own age-correlated structure rather than the modules. The orientation columns give the second reason: the switch axis of a gene is fitted independently in each cohort, and about 45% of the genes that can be oriented (2,505–2,616 of 5,450–5,739 per region) carry the opposite sign in the two cohorts, so a raw projected coefficient inherits a sign the projection did not earn. These columns are empty for WGCNA, which projects abundance features and has no switch axis to orient.</t>
         </is>
       </c>
     </row>
